--- a/artfynd/A 65637-2020 artfynd.xlsx
+++ b/artfynd/A 65637-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 65637-2020 artfynd.xlsx
+++ b/artfynd/A 65637-2020 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>84275372</v>
       </c>
       <c r="B2" t="n">
-        <v>106600</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>631501.416918454</v>
+        <v>631501</v>
       </c>
       <c r="R2" t="n">
-        <v>6838144.031586658</v>
+        <v>6838144</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,19 +748,9 @@
           <t>2006-07-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2006-07-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 65637-2020 artfynd.xlsx
+++ b/artfynd/A 65637-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84275372</v>
       </c>
       <c r="B2" t="n">
-        <v>109041</v>
+        <v>109050</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 65637-2020 artfynd.xlsx
+++ b/artfynd/A 65637-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84275372</v>
       </c>
       <c r="B2" t="n">
-        <v>109050</v>
+        <v>109063</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 65637-2020 artfynd.xlsx
+++ b/artfynd/A 65637-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84275372</v>
       </c>
       <c r="B2" t="n">
-        <v>109063</v>
+        <v>109072</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 65637-2020 artfynd.xlsx
+++ b/artfynd/A 65637-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84275372</v>
       </c>
       <c r="B2" t="n">
-        <v>109072</v>
+        <v>109077</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 65637-2020 artfynd.xlsx
+++ b/artfynd/A 65637-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84275372</v>
       </c>
       <c r="B2" t="n">
-        <v>109077</v>
+        <v>109105</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 65637-2020 artfynd.xlsx
+++ b/artfynd/A 65637-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84275372</v>
       </c>
       <c r="B2" t="n">
-        <v>109105</v>
+        <v>109111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 65637-2020 artfynd.xlsx
+++ b/artfynd/A 65637-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84275372</v>
       </c>
       <c r="B2" t="n">
-        <v>109111</v>
+        <v>109118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 65637-2020 artfynd.xlsx
+++ b/artfynd/A 65637-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84275372</v>
       </c>
       <c r="B2" t="n">
-        <v>109118</v>
+        <v>109122</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 65637-2020 artfynd.xlsx
+++ b/artfynd/A 65637-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84275372</v>
       </c>
       <c r="B2" t="n">
-        <v>109122</v>
+        <v>109130</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 65637-2020 artfynd.xlsx
+++ b/artfynd/A 65637-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84275372</v>
       </c>
       <c r="B2" t="n">
-        <v>109133</v>
+        <v>109138</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 65637-2020 artfynd.xlsx
+++ b/artfynd/A 65637-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84275372</v>
       </c>
       <c r="B2" t="n">
-        <v>109138</v>
+        <v>109146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
